--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_metropolitana.xlsx
@@ -54,12 +54,12 @@
     <t xml:space="preserve">Cerro Navia</t>
   </si>
   <si>
+    <t xml:space="preserve">Isla de Maipo</t>
+  </si>
+  <si>
     <t xml:space="preserve">María Pinto</t>
   </si>
   <si>
-    <t xml:space="preserve">Isla de Maipo</t>
-  </si>
-  <si>
     <t xml:space="preserve">Lo Espejo</t>
   </si>
   <si>
@@ -123,12 +123,12 @@
     <t xml:space="preserve">Santiago</t>
   </si>
   <si>
+    <t xml:space="preserve">Pudahuel</t>
+  </si>
+  <si>
     <t xml:space="preserve">Puente Alto</t>
   </si>
   <si>
-    <t xml:space="preserve">Pudahuel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Calera de Tango</t>
   </si>
   <si>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:27</t>
+    <t xml:space="preserve">2026-09-09 23:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -733,7 +733,7 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>13504</v>
+        <v>13603</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2021</v>
@@ -750,7 +750,7 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>13603</v>
+        <v>13504</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2021</v>
@@ -1124,7 +1124,7 @@
         <v>35</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>13201</v>
+        <v>13124</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>2021</v>
@@ -1141,7 +1141,7 @@
         <v>36</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>13124</v>
+        <v>13201</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>2021</v>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:24</t>
+    <t xml:space="preserve">2026-09-17 14:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_metropolitana.xlsx
@@ -54,12 +54,12 @@
     <t xml:space="preserve">Cerro Navia</t>
   </si>
   <si>
+    <t xml:space="preserve">María Pinto</t>
+  </si>
+  <si>
     <t xml:space="preserve">Isla de Maipo</t>
   </si>
   <si>
-    <t xml:space="preserve">María Pinto</t>
-  </si>
-  <si>
     <t xml:space="preserve">Lo Espejo</t>
   </si>
   <si>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:20</t>
+    <t xml:space="preserve">2026-09-23 12:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -733,7 +733,7 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>13603</v>
+        <v>13504</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2021</v>
@@ -750,7 +750,7 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>13504</v>
+        <v>13603</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2021</v>
@@ -1500,7 +1500,9 @@
       <c r="C53" s="2" t="n">
         <v>13303</v>
       </c>
-      <c r="D53" s="2"/>
+      <c r="D53" s="2" t="n">
+        <v>2021</v>
+      </c>
       <c r="E53" s="2"/>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_metropolitana.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
   <si>
     <t xml:space="preserve">Región</t>
   </si>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:48</t>
+    <t xml:space="preserve">2026-10-01 23:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -219,7 +219,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Ingreso sobre la mediana nacional (%)</t>
+    <t xml:space="preserve">% bajo 50% de la mediana</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>
@@ -232,9 +232,6 @@
   </si>
   <si>
     <t xml:space="preserve">Unidad de medida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% sobre mediana</t>
   </si>
 </sst>
 </file>
@@ -1582,7 +1579,7 @@
         <v>71</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:07</t>
+    <t xml:space="preserve">2026-10-02 11:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 11:20</t>
+    <t xml:space="preserve">2026-10-02 15:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:12</t>
+    <t xml:space="preserve">2026-10-05 12:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
